--- a/paper/supplementary_material.xlsx
+++ b/paper/supplementary_material.xlsx
@@ -13,12 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4_matched_arm" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5_size_sensitivity" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6_seed_stability" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_financ_modeA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_financ_modeB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_gamifi_modeA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_gamifi_modeB" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_manage_modeA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_manage_modeB" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6b_consensus" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_financ_modeA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_financ_modeB" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_gamifi_modeA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_gamifi_modeB" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_manage_modeA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_manage_modeB" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,6 +599,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>gap_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>keyword_display</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cluster_label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>n_articles</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>citations</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>article_titles</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>article_dois</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>metric_distance_from_centroid</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>metric_cluster_threshold</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>metric_centrality</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>metric_tfidf</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metric_citations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Time poverty</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USE model &amp; Value</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5935756379996343</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>distance 0.5936 exceeds the cluster-5 p95 threshold 0.5538; frequency=1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>How Does Gamification Improve Purchase Intention? Through the Lens of Perceived Brand Coolness and Time Poverty</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10.3390/bs14121226</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5935756379996343</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5538393465792733</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6170421681475498</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0031771567761825</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Instructional strategy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Elemental tetrad model &amp; Hedonic motivation</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5143948213891975</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>distance 0.5144 exceeds the cluster-6 p95 threshold 0.5144; frequency=1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Gamification using a choose-your-own-adventure type platform to augment learning and facilitate student engagement in marketing education</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0.5143948213891975</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5143948213891975</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5835228111533514</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0038123520314961</v>
+      </c>
+      <c r="O3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>User participation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Customer engagement &amp; Consumer–brand engagement</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4028139246678535</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>distance 0.4028 exceeds the cluster-4 p95 threshold 0.4028; frequency=1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The role of user participation and psychological distance in consumer brand attitudes in gamified marketing</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-024-84268-5</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4028139246678535</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4027916206340033</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4185383247537805</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0028040989758205</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marketing effectiveness</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer buying intentions &amp; consumer experience</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4027102547267941</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>distance 0.4027 exceeds the cluster-7 p95 threshold 0.3988; frequency=1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>How gamified branded applications drive marketing effectiveness?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.1108/MIP-09-2020-0407</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4027102547267941</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3987942549447737</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4025488076321397</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0032320848985656</v>
+      </c>
+      <c r="O5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Impulse buying</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Customer buying intentions &amp; consumer experience</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3989995973158876</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>distance 0.3990 exceeds the cluster-7 p95 threshold 0.3988; frequency=1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>It’s not all fun and games: gamification in e-commerce on consumers’ impulse buying of retail food products</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10.1108/BFJ-04-2024-0361</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3989995973158876</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3987942549447737</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4663771638588663</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0030807718229092</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Peripheral Keyword</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Game elements</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gamification in marketing &amp; gamification marketing</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3640547381007739</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>distance 0.3641 exceeds the cluster-1 p95 threshold 0.3588; frequency=1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EMPIRICAL STUDY ON GAMIFICATION EFFECT ON BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10.51847/sAorvxedSs</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3640547381007739</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3587503031023259</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5328054804625619</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0030641998720734</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2465,7 +2907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2910,7 +3352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4740,7 +5182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4816,40 +5258,45 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>frequency_threshold</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>peripheral_share</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>n_core_domain_terms</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>core_domain_terms</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>gaps_before_dedup</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>gaps_after_dedup</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>tfidf_match_types</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>article_encoder</t>
         </is>
@@ -4908,26 +5355,27 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>digital transformation, dynamic capabilities</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>38</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>27</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>{"exact": 139, "contains": 7}</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>{"encoder": "precomputed", "model": null}</t>
         </is>
@@ -4984,28 +5432,29 @@
           <t>{"0": 30, "1": 27, "2": 28, "3": 17, "4": 30, "5": 14}</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.0410958904109589</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>digital transformation, dynamic capabilities</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>{"exact": 139, "contains": 7}</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -5064,26 +5513,27 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>financial inclusion, fintech</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>39</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>27</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>{"exact": 164, "contains": 4}</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>{"encoder": "precomputed", "model": null}</t>
         </is>
@@ -5140,28 +5590,29 @@
           <t>{"0": 15, "1": 27, "2": 31, "3": 37, "4": 30, "5": 28}</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>financial inclusion, fintech</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>{"exact": 164, "contains": 4}</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -5220,26 +5671,27 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>gamification</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>39</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>28</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>{"exact": 169, "contains": 3}</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>{"encoder": "precomputed", "model": null}</t>
         </is>
@@ -5298,28 +5750,29 @@
           <t>{"0": 35, "1": 18, "2": 15, "3": 16, "4": 15, "5": 30, "6": 21, "7": 22}</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.03488372093023256</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>gamification</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
         <is>
           <t>{"exact": 169, "contains": 3}</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -5336,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5417,35 +5870,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>permutation_p</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>cohens_d</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>n_nested_judgements_removed</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>fleiss_kappa</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>krippendorff_alpha</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>leaveout_spearman_rho</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>leaveout_spearman_p</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>leaveout_label_agreement</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>annotator_failures</t>
         </is>
@@ -5466,60 +5929,66 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>858</v>
+        <v>728</v>
       </c>
       <c r="G2" t="n">
         <v>0.4615384615384616</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4711538461538461</v>
+        <v>0.4732441471571907</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9615384615384581</v>
+        <v>-1.170568561872909</v>
       </c>
       <c r="J2" t="n">
         <v>3.153846153846154</v>
       </c>
       <c r="K2" t="n">
-        <v>3.263736263736264</v>
+        <v>3.277591973244147</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.367003367003369</v>
+        <v>-3.775510204081637</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5654504487785841</v>
+        <v>-0.6252392797859059</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5724623616812525</v>
+        <v>0.5325446134029778</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6321943071648644</v>
+        <v>0.6199686091129925</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05310738869894643</v>
+        <v>0.5494225288735564</v>
       </c>
       <c r="Q2" t="n">
+        <v>-0.05964775964740349</v>
+      </c>
+      <c r="R2" t="n">
+        <v>130</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.5785755757693051</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>0.5643458826548586</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.7606517185025122</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>6.472989368668696e-06</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5540,60 +6009,66 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>758</v>
+        <v>728</v>
       </c>
       <c r="G3" t="n">
         <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4711538461538461</v>
+        <v>0.4799426934097421</v>
       </c>
       <c r="I3" t="n">
-        <v>-7.115384615384612</v>
+        <v>-7.994269340974208</v>
       </c>
       <c r="J3" t="n">
         <v>2.866666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>3.263736263736264</v>
+        <v>3.306590257879656</v>
       </c>
       <c r="L3" t="n">
-        <v>-12.16610549943883</v>
+        <v>-13.30444829578279</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.040154701705771</v>
+        <v>-1.151081880746093</v>
       </c>
       <c r="N3" t="n">
-        <v>0.306163713331373</v>
+        <v>0.2582972414335886</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2109901799461182</v>
+        <v>0.1766997515188796</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1910839143914727</v>
+        <v>0.2782360881955902</v>
       </c>
       <c r="Q3" t="n">
+        <v>-0.2110686143551978</v>
+      </c>
+      <c r="R3" t="n">
+        <v>30</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.6534653465346533</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.8446099459802987</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5614,60 +6089,66 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>957</v>
+        <v>838</v>
       </c>
       <c r="G4" t="n">
         <v>0.6470588235294118</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5429594272076372</v>
+        <v>0.5201668984700973</v>
       </c>
       <c r="I4" t="n">
-        <v>10.40993963217746</v>
+        <v>12.68919250593145</v>
       </c>
       <c r="J4" t="n">
         <v>4.025210084033613</v>
       </c>
       <c r="K4" t="n">
-        <v>3.705250596658711</v>
+        <v>3.577190542420028</v>
       </c>
       <c r="L4" t="n">
-        <v>8.635299530440191</v>
+        <v>12.52434099611851</v>
       </c>
       <c r="M4" t="n">
-        <v>1.557795634118998</v>
+        <v>2.159927229721272</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1212213886764707</v>
+        <v>0.03218608097796782</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06573496052980847</v>
+        <v>0.01408206355388826</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1460376743085046</v>
+        <v>0.04589770511474426</v>
       </c>
       <c r="Q4" t="n">
+        <v>0.2061612507276378</v>
+      </c>
+      <c r="R4" t="n">
+        <v>119</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.7029778182923125</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.6249200866882899</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.8301898926809501</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>5.198019522721792e-07</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5688,60 +6169,66 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="G5" t="n">
         <v>0.45</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5429594272076372</v>
+        <v>0.5427872860635696</v>
       </c>
       <c r="I5" t="n">
-        <v>-9.295942720763723</v>
+        <v>-9.278728606356962</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.705250596658711</v>
+        <v>3.711491442542787</v>
       </c>
       <c r="L5" t="n">
-        <v>-10.93719806763285</v>
+        <v>-11.08695652173914</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9536473209971824</v>
+        <v>-0.9677379495349481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3514187575439821</v>
+        <v>0.3444739626387991</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7075753336075024</v>
+        <v>0.7132500447149484</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1929484960994009</v>
+        <v>0.4394780260986951</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.1953181520282271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.4488188976377953</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.476639344262295</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.8</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.5</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5762,60 +6249,66 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>990</v>
+        <v>860</v>
       </c>
       <c r="G6" t="n">
         <v>0.3538461538461539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4372093023255814</v>
+        <v>0.4452054794520548</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.336314847942756</v>
+        <v>-9.135932560590094</v>
       </c>
       <c r="J6" t="n">
         <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.026744186046511</v>
+        <v>3.056164383561644</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.491356127545139</v>
+        <v>-8.381891528462573</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.257261480152995</v>
+        <v>-1.402050630334113</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2103585260151626</v>
+        <v>0.1626104579216653</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1781146986428058</v>
+        <v>0.149088351241044</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1172641313095639</v>
+        <v>0.175691215439228</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.1320683382412542</v>
+      </c>
+      <c r="R6" t="n">
+        <v>130</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.5350685475859333</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.3750012605202337</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.641165550015072</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0004163393643346803</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5836,60 +6329,66 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="G7" t="n">
         <v>0.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4372093023255814</v>
+        <v>0.4349397590361446</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.720930232558139</v>
+        <v>-3.493975903614455</v>
       </c>
       <c r="J7" t="n">
         <v>3.133333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>3.026744186046511</v>
+        <v>3.013253012048193</v>
       </c>
       <c r="L7" t="n">
-        <v>3.521577666794731</v>
+        <v>3.985072637611618</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2538901351248453</v>
+        <v>0.2859334919072402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8012830351851604</v>
+        <v>0.7768583401970557</v>
       </c>
       <c r="O7" t="n">
-        <v>0.96184804410408</v>
+        <v>0.9859043008954801</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05029643051361679</v>
+        <v>0.7790610469476527</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.05678731147234063</v>
+      </c>
+      <c r="R7" t="n">
+        <v>30</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.5392491467576793</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.5208914087723443</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.8116794499134279</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.04985758510134036</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.5</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -5906,7 +6405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5922,12 +6421,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_eligible_pool</t>
+          <t>n_eligible_annotated</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>n_eligible_annotated</t>
+          <t>n_not_eligible</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -5971,6 +6470,11 @@
         </is>
       </c>
       <c r="M1" t="inlineStr">
+        <is>
+          <t>permutation_p</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>cohens_d</t>
         </is>
@@ -5984,41 +6488,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>selected vs eligible</t>
+          <t>eligible vs not eligible</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5223214285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5223214285714286</v>
+        <v>0.4438502673796791</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.078296703296704</v>
+        <v>7.847116119174946</v>
       </c>
       <c r="H2" t="n">
-        <v>3.153846153846154</v>
+        <v>3.441964285714286</v>
       </c>
       <c r="I2" t="n">
-        <v>3.441964285714286</v>
+        <v>3.179144385026738</v>
       </c>
       <c r="J2" t="n">
-        <v>-8.370747281253117</v>
+        <v>8.267001081340858</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1957300208365904</v>
+        <v>0.1356357142364281</v>
       </c>
       <c r="L2" t="n">
-        <v>0.126161065857947</v>
+        <v>0.01913378289772064</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1433758493531011</v>
+        <v>0.1493425328733563</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1245013368737326</v>
       </c>
     </row>
     <row r="3">
@@ -6029,41 +6536,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eligible vs all</t>
+          <t>selected vs eligible</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.5223214285714286</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.4711538461538461</v>
-      </c>
       <c r="G3" t="n">
-        <v>5.116758241758246</v>
+        <v>-6.078296703296704</v>
       </c>
       <c r="H3" t="n">
+        <v>3.153846153846154</v>
+      </c>
+      <c r="I3" t="n">
         <v>3.441964285714286</v>
       </c>
-      <c r="I3" t="n">
-        <v>3.263736263736264</v>
-      </c>
       <c r="J3" t="n">
-        <v>5.460858585858584</v>
+        <v>-8.370747281253117</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2485959199050884</v>
+        <v>0.1957300208365904</v>
       </c>
       <c r="L3" t="n">
-        <v>0.116898626253424</v>
+        <v>0.126161065857947</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08692352001807419</v>
+        <v>0.191540422978851</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1433758493531011</v>
       </c>
     </row>
     <row r="4">
@@ -6074,41 +6584,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>selected vs eligible</t>
+          <t>eligible vs not eligible</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.5785953177257525</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5785953177257525</v>
+        <v>0.4725536992840095</v>
       </c>
       <c r="G4" t="n">
-        <v>6.846350580365934</v>
+        <v>10.60416184417429</v>
       </c>
       <c r="H4" t="n">
-        <v>4.025210084033613</v>
+        <v>3.705685618729097</v>
       </c>
       <c r="I4" t="n">
-        <v>3.705685618729097</v>
+        <v>3.393794749403341</v>
       </c>
       <c r="J4" t="n">
-        <v>8.622546491520788</v>
+        <v>9.190033350737812</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1518206103241466</v>
+        <v>0.05936571581414934</v>
       </c>
       <c r="L4" t="n">
-        <v>0.169214533475869</v>
+        <v>0.0008412593132672171</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1567597667970911</v>
+        <v>0.06864656767161642</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1408738243179334</v>
       </c>
     </row>
     <row r="5">
@@ -6119,41 +6632,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eligible vs all</t>
+          <t>selected vs eligible</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E5" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.5785953177257525</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.5429594272076372</v>
-      </c>
       <c r="G5" t="n">
-        <v>3.563589051811522</v>
+        <v>6.846350580365934</v>
       </c>
       <c r="H5" t="n">
+        <v>4.025210084033613</v>
+      </c>
+      <c r="I5" t="n">
         <v>3.705685618729097</v>
       </c>
-      <c r="I5" t="n">
-        <v>3.705250596658711</v>
-      </c>
       <c r="J5" t="n">
-        <v>0.01174069226999698</v>
+        <v>8.622546491520788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9975409279489842</v>
+        <v>0.1518206103241466</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3576875890414073</v>
+        <v>0.169214533475869</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002008139066363647</v>
+        <v>0.1498425078746063</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1567597667970911</v>
       </c>
     </row>
   </sheetData>
@@ -7366,320 +7882,516 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>gap_type</t>
+          <t>corpus</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>keyword_display</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cluster_label</t>
+          <t>pooling</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>n_seeds</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>n_articles</t>
+          <t>corpus_sizes</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>citations</t>
+          <t>n_candidates_pooled</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>n_majority_support</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>article_titles</t>
+          <t>n_unanimous</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>article_dois</t>
+          <t>mean_pairwise_jaccard</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>metric_distance_from_centroid</t>
+          <t>min_pairwise_jaccard</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>metric_cluster_threshold</t>
+          <t>max_pairwise_jaccard</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>metric_centrality</t>
+          <t>mean_jaccard_same_size</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>metric_tfidf</t>
+          <t>mean_jaccard_across_sizes</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>metric_citations</t>
+          <t>mean_candidates_per_run</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Account ownership</t>
+          <t>articles_first</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alternative credit &amp; Bigtech credit</t>
+          <t>seeds_only</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.550055776382103</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[50]</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>distance 0.5501 exceeds the cluster-1 p95 threshold 0.5124; frequency=1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Has financial inclusion made the financial sector riskier?</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10.1108/JFRC-08-2020-0074</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.441153169323901</v>
       </c>
       <c r="K2" t="n">
-        <v>0.550055776382103</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5123804576149628</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5531460811628005</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0020072232246325</v>
-      </c>
+        <v>0.441153169323901</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>51</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Social responsibilities</t>
+          <t>articles_first</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Credit risk &amp; Bank credit risk</t>
+          <t>seeds_and_sizes</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4899835996796744</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[30, 50, 100, 150]</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>distance 0.4900 exceeds the cluster-4 p95 threshold 0.4887; frequency=1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Digital Inclusion and Financial Inclusion: Evidence from Peer-to-Peer Lending</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10.1007/s10551-024-05689-w</t>
-        </is>
+        <v>161</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2335238143816472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4899835996796744</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4886575456317839</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5621745500823818</v>
+        <v>0.4509687234631418</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0027922466469821</v>
+        <v>0.1755385052932487</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digital inclusion</t>
+          <t>keywords_first</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bank FinTech &amp; Fintech credit</t>
+          <t>seeds_only</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.427087994201441</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[50]</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>distance 0.4271 exceeds the cluster-2 p95 threshold 0.3983; frequency=1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Digital Inclusion and Financial Inclusion: Evidence from Peer-to-Peer Lending</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10.1007/s10551-024-05689-w</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1400793650793651</v>
       </c>
       <c r="K4" t="n">
-        <v>0.427087994201441</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3982909043116323</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4809732307086573</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0027922466469821</v>
-      </c>
+        <v>0.1400793650793651</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digital economy</t>
+          <t>keywords_first</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bank FinTech &amp; Fintech credit</t>
+          <t>seeds_and_sizes</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4143741738335522</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[30, 50, 100, 150]</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>distance 0.4144 exceeds the cluster-2 p95 threshold 0.3983; frequency=1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>How Does Fintech Affect the Development of the Digital Economy? Evidence from India</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10.1007/s13132-024-02547-y</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.157911518968791</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4143741738335522</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3982909043116323</v>
+        <v>0.5625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4408055289145633</v>
+        <v>0.2882226474505886</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0037652643216191</v>
+        <v>0.1231618847069783</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Economics &amp; finance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>articles_first</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>seeds_only</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[50]</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>57</v>
+      </c>
+      <c r="H6" t="n">
+        <v>19</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3815741059162112</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3815741059162112</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Economics &amp; finance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>articles_first</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>seeds_and_sizes</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[30, 50, 100, 150]</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>166</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1939731684583125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3845310461131619</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1431577344170193</v>
+      </c>
+      <c r="O7" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Economics &amp; finance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>keywords_first</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>seeds_only</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[50]</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1511904761904762</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1511904761904762</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Economics &amp; finance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>keywords_first</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>seeds_and_sizes</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[30, 50, 100, 150]</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1402040941514626</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2615601412476412</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1078424815924816</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7693,7 +8405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7749,12 +8461,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>metric_distance_from_subcentroid</t>
+          <t>metric_distance_from_centroid</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>metric_distance_zscore</t>
+          <t>metric_cluster_threshold</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -7769,1718 +8481,245 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>metric_global_frequency</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>metric_similarity</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>metric_frequency_1</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>metric_frequency_2</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>metric_mean_tfidf</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>metric_frequency_other_clusters</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>metric_presence_ratio</t>
+          <t>metric_citations</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Conceptual Combination</t>
+          <t>Peripheral Keyword</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Credit risk x Financial inclusion</t>
+          <t>Account ownership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Credit risk &amp; Financial technology</t>
+          <t>Alternative credit &amp; Bigtech credit</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7117009979166558</v>
+        <v>0.550055776382103</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>semantically related (similarity=0.35) but never co-occurring; mean tfidf=0.0307</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0.3495737563322701</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.0306806642836131</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>distance 0.5501 exceeds the cluster-1 p95 threshold 0.5124; frequency=1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Has financial inclusion made the financial sector riskier?</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10.1108/JFRC-08-2020-0074</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.550055776382103</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5123804576149628</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5531460811628005</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0020072232246325</v>
+      </c>
+      <c r="O2" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Conceptual Combination</t>
+          <t>Peripheral Keyword</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Credit risk x Fintech credit</t>
+          <t>Social responsibilities</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Credit risk &amp; Financial technology</t>
+          <t>Credit risk &amp; Bank credit risk</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6420377078669098</v>
+        <v>0.4899835996796744</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>semantically related (similarity=0.46) but never co-occurring; mean tfidf=0.0129</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0.4583331394828586</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.0129014064843989</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>distance 0.4900 exceeds the cluster-4 p95 threshold 0.4887; frequency=1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Digital Inclusion and Financial Inclusion: Evidence from Peer-to-Peer Lending</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10.1007/s10551-024-05689-w</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4899835996796744</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4886575456317839</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5621745500823818</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0027922466469821</v>
+      </c>
+      <c r="O3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Conceptual Combination</t>
+          <t>Peripheral Keyword</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Commercial banks x Financial inclusion</t>
+          <t>Digital inclusion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Credit risk &amp; Financial technology</t>
+          <t>Bank FinTech &amp; Fintech credit</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6354584834575043</v>
+        <v>0.427087994201441</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>semantically related (similarity=0.39) but never co-occurring; mean tfidf=0.0239</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0.3923224875803229</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.0238668311310819</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>distance 0.4271 exceeds the cluster-2 p95 threshold 0.3983; frequency=1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Digital Inclusion and Financial Inclusion: Evidence from Peer-to-Peer Lending</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10.1007/s10551-024-05689-w</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.427087994201441</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3982909043116323</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4809732307086573</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0027922466469821</v>
+      </c>
+      <c r="O4" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conceptual Combination</t>
+          <t>Peripheral Keyword</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial technology x Financial innovation</t>
+          <t>Digital economy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial technology &amp; financial innovation</t>
+          <t>Bank FinTech &amp; Fintech credit</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4279138072466339</v>
+        <v>0.4143741738335522</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>semantically related (similarity=0.62) but never co-occurring; mean tfidf=0.0137</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0.6163971870838265</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0136771856378983</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Banks’ risk-taking</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6375290038949116</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>195</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>absent from cluster 0, present in 1 record(s) elsewhere (2.0% of corpus), tfidf=0.0282</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Fintech-based financial inclusion and bank risk-taking: Evidence from OIC countries</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>10.1016/j.intfin.2021.101447</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>0.0281871122181571</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Financial innovation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5842158444101582</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>51</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>absent from cluster 0, present in 3 record(s) elsewhere (6.0% of corpus), tfidf=0.0121</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Promise (Un)Kept? Fintech and Financial Inclusion | THE ROLE OF FINANCIAL TECHNOLOGY IN ENHANCING FINANCIAL INCLUSION: A REGULATORY PERSPECTIVE ON CURRENT INDUSTRY TRENDS | Has financial inclusion made the financial sector riskier?</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>10.1111/sjpe.70012 | 10.22495/cbsrv6i1art4 | 10.1108/JFRC-08-2020-0074</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0.0121283396500148</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5437422783212031</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>143</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>absent from cluster 0, present in 3 record(s) elsewhere (6.0% of corpus), tfidf=0.0075</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa | Fintech-based Financial Inclusion and Risk-taking of Microfinance Institutions (MFIs): Evidence from Sub-Saharan Africa | Fintech-based financial inclusion and banks' risk-taking: the role of regulation in Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10.1080/23322039.2024.2375643 | 10.1016/j.frl.2021.102149 | 10.1108/JEAS-11-2023-0304</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.0074629096558344</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Inclusive finance</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Financial technology</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.521988790200158</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>19</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>absent from cluster 2, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0099</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Inclusive FinTech, open banking, and bank performance: evidence from China | Does Fintech-Driven Inclusive Finance Induce Bank Profitability? Empirical Evidence from Developing Countries</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10.1186/s40854-024-00679-3 | 10.3390/jrfm16100457</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.0099120171442609</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Commercial banks</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; financial innovation</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5048861925315545</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>424</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>absent from cluster 1, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0079</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Does bank FinTech reduce credit risk? Evidence from China | The impact of bank FinTech on commercial banks' risk-taking in China</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10.1016/j.pacfin.2020.101398 | 10.1016/j.irfa.2023.102944</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.0079405829502457</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bigtech credit</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5018263514129284</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>absent from cluster 5, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0076</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa | Digital disruption in financing: Are fintech and bigtech credit reshaping corporate access to capital?</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10.1080/23322039.2024.2375643 | 10.1016/j.intfin.2025.102198</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.007587871886909</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cross-Cluster Concept</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bank FinTech</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4979370700342781</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>424</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>absent from cluster 5, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0071</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Does bank FinTech reduce credit risk? Evidence from China | Bank FinTech and credit risk: comparison of selected emerging and developed countries</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>10.1016/j.pacfin.2020.101398 | 10.1108/SEF-12-2023-0714</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.0071395503834397</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>South Asia</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Panel data &amp; Alternative information</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.7700000345845694</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.79, tfidf=0.0037</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Financial inclusion based on financial technology and risky behaviour of micro-finance institutes: evidence from South Asian micro-finance banks</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10.1108/DPRG-12-2022-0149</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0.5212219373641441</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.789004278823916</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.6239581577926591</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.0036556225742735</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Soft information</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Financial technology</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.7446672439035917</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
+          <t>distance 0.4144 exceeds the cluster-2 p95 threshold 0.3983; frequency=1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>How Does Fintech Affect the Development of the Digital Economy? Evidence from India</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.1007/s13132-024-02547-y</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4143741738335522</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3982909043116323</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4408055289145633</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0037652643216191</v>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=2.22, tfidf=0.0033</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Bridging the gap? A theoretical analysis of the net effect of FinTech entry on access to credit</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>10.1016/j.frl.2024.105918</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0.552898914292175</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2.218196276542958</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.5852382263997589</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.0033112831905381</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Regulatory resources</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; financial innovation</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.7162890749999427</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.85, tfidf=0.0038</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>How Does Fintech Affect the Development of the Digital Economy? Evidence from India</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>10.1007/s13132-024-02547-y</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0.4588934313631362</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.850259048960978</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.5085676388929534</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0037652643216191</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Debt trap</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.7055597185654363</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>391</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.04, tfidf=0.0036</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>The rise of digital finance: Financial inclusion or debt trap?</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>10.1016/j.frl.2021.102604</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>0.2785436570909961</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.038449517511149</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.5076362885186358</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.0035500266524496</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Financial technology</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 3 in corpus, z=2.27, tfidf=0.0075</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>10.1080/23322039.2024.2375643</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0.5581178530369838</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.267854053430929</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.6771015424689225</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.0074629096558344</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Alternative data</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Financial technology</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.6943181050235157</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=0.34, tfidf=0.0061</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>The role of bank–FinTech partnerships in creating a more inclusive banking system</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>10.21799/frbp.wp.2023.21</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.3554167823487117</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.3391698830709926</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.3919594342963742</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.0061423532230996</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Risk-taking behavior</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.6822459914777559</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>143</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=2.05, tfidf=0.0030</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Fintech-based Financial Inclusion and Risk-taking of Microfinance Institutions (MFIs): Evidence from Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>10.1016/j.frl.2021.102149</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0.4160403358280311</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.048529493785347</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.5828420140215937</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.0029862148015119</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; financial innovation</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6661038066192673</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=0.66, tfidf=0.0041</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>DOES FINTECH AFFECT FINANCIAL INCLUSION IN BALKAN REGION COUNTRIES?</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>10.22495/jgrv13i1siart12</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>0.3501876271531672</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.6596497095801059</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.5476971165331981</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.0041047638465623</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Disadvantaged Communities</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; financial innovation</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.6630721459130551</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>19</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=0.29, tfidf=0.0055</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>THE ROLE OF FINANCIAL TECHNOLOGY IN ENHANCING FINANCIAL INCLUSION: A REGULATORY PERSPECTIVE ON CURRENT INDUSTRY TRENDS</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>10.22495/cbsrv6i1art4</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>0.3160284105102336</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.285518055280809</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.4808629481045412</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.0054968036072316</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Banks’ risk-taking</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.6598008172085355</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>195</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=-1.16, tfidf=0.0282</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Fintech-based financial inclusion and bank risk-taking: Evidence from OIC countries</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>10.1016/j.intfin.2021.101447</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>0.1598415970482152</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-1.155809275001417</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.3830864484297354</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.0281871122181571</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bank concentration</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Panel data &amp; Alternative information</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6575478011809395</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.21, tfidf=0.0037</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Does digital financial inclusion moderate or exacerbate output volatility?</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>10.1080/13504851.2021.1963400</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0.4584609624946814</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.206184642075575</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.505308339304069</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.0036878431466645</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Black swan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Financial technology &amp; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6374958055320006</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>51</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.21, tfidf=0.0020</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Has financial inclusion made the financial sector riskier?</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>10.1108/JFRC-08-2020-0074</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0.3491909563733197</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.212428351069866</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.6635805922073728</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.0020072232246325</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Output volatility</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Panel data &amp; Alternative information</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.632986075391512</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=0.67, tfidf=0.0037</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Does digital financial inclusion moderate or exacerbate output volatility?</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>10.1080/13504851.2021.1963400</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>0.4006583175410005</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.6694097337019128</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.5322524413975456</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.0036878431466645</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Big tech</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Income inequality &amp; Big tech</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>44</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 1 in corpus, z=1.00, tfidf=0.0040</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Fintech credit, big tech credit and income inequality</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>10.1016/j.frl.2022.103387</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0.3804038906307352</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.4321319645328699</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.0039585973693234</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.5410662758628697</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 6 in corpus, z=-0.02, tfidf=0.0216</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>The impact of digitalization on credit risk: the mediating role of financial inclusion (National Bank of Egypt (NBE) case study)</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>10.1080/1331677X.2023.2178018</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>0.2159997698833071</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-0.0216513816314452</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.4261859866156499</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.0215682492553081</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Emerging Concept</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Digital lending</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Credit risk &amp; Digitalization</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.5059078686803615</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>391</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>frequency=1 in cluster, 2 in corpus, z=0.59, tfidf=0.0068</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>The rise of digital finance: Financial inclusion or debt trap?</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>10.1016/j.frl.2021.102604</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>0.2519684540715916</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.5880074699579506</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.2993909863575299</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.006790361222391</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9493,7 +8732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9549,12 +8788,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>metric_distance_from_centroid</t>
+          <t>metric_distance_from_subcentroid</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>metric_cluster_threshold</t>
+          <t>metric_distance_zscore</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -9569,260 +8808,270 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>metric_citations</t>
+          <t>metric_global_frequency</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>metric_similarity</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>metric_frequency_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>metric_frequency_2</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>metric_mean_tfidf</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>metric_frequency_other_clusters</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>metric_presence_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Conceptual Combination</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Time poverty</t>
+          <t>Credit risk x Financial inclusion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USE model &amp; Value</t>
+          <t>Credit risk &amp; Financial technology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5935756379996343</v>
+        <v>0.7117009979166558</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>distance 0.5936 exceeds the cluster-5 p95 threshold 0.5538; frequency=1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>How Does Gamification Improve Purchase Intention? Through the Lens of Perceived Brand Coolness and Time Poverty</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10.3390/bs14121226</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5935756379996343</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5538393465792733</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.6170421681475498</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0031771567761825</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
+          <t>semantically related (similarity=0.35) but never co-occurring; mean tfidf=0.0307</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0.3495737563322701</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0306806642836131</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Conceptual Combination</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Instructional strategy</t>
+          <t>Credit risk x Fintech credit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Elemental tetrad model &amp; Hedonic motivation</t>
+          <t>Credit risk &amp; Financial technology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5143948213891975</v>
+        <v>0.6420377078669098</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>distance 0.5144 exceeds the cluster-6 p95 threshold 0.5144; frequency=1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Gamification using a choose-your-own-adventure type platform to augment learning and facilitate student engagement in marketing education</t>
-        </is>
-      </c>
+          <t>semantically related (similarity=0.46) but never co-occurring; mean tfidf=0.0129</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0.5143948213891975</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5143948213891975</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5835228111533514</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0038123520314961</v>
-      </c>
-      <c r="O3" t="n">
-        <v>30</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0.4583331394828586</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0129014064843989</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Conceptual Combination</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>User participation</t>
+          <t>Commercial banks x Financial inclusion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer engagement &amp; Consumer–brand engagement</t>
+          <t>Credit risk &amp; Financial technology</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4028139246678535</v>
+        <v>0.6354584834575043</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>semantically related (similarity=0.39) but never co-occurring; mean tfidf=0.0239</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0.3923224875803229</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>distance 0.4028 exceeds the cluster-4 p95 threshold 0.4028; frequency=1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>The role of user participation and psychological distance in consumer brand attitudes in gamified marketing</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-024-84268-5</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.4028139246678535</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.4027916206340033</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.4185383247537805</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0028040989758205</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0238668311310819</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Conceptual Combination</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marketing effectiveness</t>
+          <t>Financial technology x Financial innovation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer buying intentions &amp; consumer experience</t>
+          <t>Financial technology &amp; financial innovation</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4027102547267941</v>
+        <v>0.4279138072466339</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>distance 0.4027 exceeds the cluster-7 p95 threshold 0.3988; frequency=1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>How gamified branded applications drive marketing effectiveness?</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10.1108/MIP-09-2020-0407</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.4027102547267941</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.3987942549447737</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.4025488076321397</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.0032320848985656</v>
-      </c>
-      <c r="O5" t="n">
-        <v>29</v>
-      </c>
+          <t>semantically related (similarity=0.62) but never co-occurring; mean tfidf=0.0137</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0.6163971870838265</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0136771856378983</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Cross-Cluster Concept</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Impulse buying</t>
+          <t>Banks’ risk-taking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Customer buying intentions &amp; consumer experience</t>
+          <t>Credit risk &amp; Digitalization</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3989995973158876</v>
+        <v>0.6375290038949116</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -9831,97 +9080,1446 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>distance 0.3990 exceeds the cluster-7 p95 threshold 0.3988; frequency=1</t>
+          <t>absent from cluster 0, present in 1 record(s) elsewhere (2.0% of corpus), tfidf=0.0282</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>It’s not all fun and games: gamification in e-commerce on consumers’ impulse buying of retail food products</t>
+          <t>Fintech-based financial inclusion and bank risk-taking: Evidence from OIC countries</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.1108/BFJ-04-2024-0361</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.3989995973158876</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3987942549447737</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4663771638588663</v>
-      </c>
+          <t>10.1016/j.intfin.2021.101447</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.0030807718229092</v>
-      </c>
-      <c r="O6" t="n">
-        <v>14</v>
+        <v>0.0281871122181571</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Peripheral Keyword</t>
+          <t>Cross-Cluster Concept</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Game elements</t>
+          <t>Financial innovation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gamification in marketing &amp; gamification marketing</t>
+          <t>Credit risk &amp; Digitalization</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3640547381007739</v>
+        <v>0.5842158444101582</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
+        <v>51</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>absent from cluster 0, present in 3 record(s) elsewhere (6.0% of corpus), tfidf=0.0121</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Promise (Un)Kept? Fintech and Financial Inclusion | THE ROLE OF FINANCIAL TECHNOLOGY IN ENHANCING FINANCIAL INCLUSION: A REGULATORY PERSPECTIVE ON CURRENT INDUSTRY TRENDS | Has financial inclusion made the financial sector riskier?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10.1111/sjpe.70012 | 10.22495/cbsrv6i1art4 | 10.1108/JFRC-08-2020-0074</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0.0121283396500148</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cross-Cluster Concept</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Digitalization</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5437422783212031</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>143</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>absent from cluster 0, present in 3 record(s) elsewhere (6.0% of corpus), tfidf=0.0075</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa | Fintech-based Financial Inclusion and Risk-taking of Microfinance Institutions (MFIs): Evidence from Sub-Saharan Africa | Fintech-based financial inclusion and banks' risk-taking: the role of regulation in Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10.1080/23322039.2024.2375643 | 10.1016/j.frl.2021.102149 | 10.1108/JEAS-11-2023-0304</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0.0074629096558344</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cross-Cluster Concept</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Inclusive finance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Financial technology</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.521988790200158</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>absent from cluster 2, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0099</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Inclusive FinTech, open banking, and bank performance: evidence from China | Does Fintech-Driven Inclusive Finance Induce Bank Profitability? Empirical Evidence from Developing Countries</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10.1186/s40854-024-00679-3 | 10.3390/jrfm16100457</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0.0099120171442609</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cross-Cluster Concept</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Commercial banks</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; financial innovation</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5048861925315545</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>424</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>absent from cluster 1, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0079</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Does bank FinTech reduce credit risk? Evidence from China | The impact of bank FinTech on commercial banks' risk-taking in China</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10.1016/j.pacfin.2020.101398 | 10.1016/j.irfa.2023.102944</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>0.0079405829502457</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cross-Cluster Concept</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bigtech credit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5018263514129284</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>absent from cluster 5, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0076</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa | Digital disruption in financing: Are fintech and bigtech credit reshaping corporate access to capital?</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10.1080/23322039.2024.2375643 | 10.1016/j.intfin.2025.102198</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>0.007587871886909</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cross-Cluster Concept</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bank FinTech</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4979370700342781</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>424</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>absent from cluster 5, present in 2 record(s) elsewhere (4.0% of corpus), tfidf=0.0071</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Does bank FinTech reduce credit risk? Evidence from China | Bank FinTech and credit risk: comparison of selected emerging and developed countries</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10.1016/j.pacfin.2020.101398 | 10.1108/SEF-12-2023-0714</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>0.0071395503834397</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Panel data &amp; Alternative information</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7700000345845694</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.79, tfidf=0.0037</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Financial inclusion based on financial technology and risky behaviour of micro-finance institutes: evidence from South Asian micro-finance banks</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10.1108/DPRG-12-2022-0149</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5212219373641441</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.789004278823916</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6239581577926591</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0036556225742735</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Soft information</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Financial technology</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7446672439035917</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=2.22, tfidf=0.0033</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Bridging the gap? A theoretical analysis of the net effect of FinTech entry on access to credit</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10.1016/j.frl.2024.105918</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.552898914292175</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.218196276542958</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5852382263997589</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0033112831905381</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Regulatory resources</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; financial innovation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7162890749999427</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.85, tfidf=0.0038</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>How Does Fintech Affect the Development of the Digital Economy? Evidence from India</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10.1007/s13132-024-02547-y</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.4588934313631362</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.850259048960978</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5085676388929534</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0037652643216191</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Debt trap</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Digitalization</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7055597185654363</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>391</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.04, tfidf=0.0036</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>The rise of digital finance: Financial inclusion or debt trap?</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10.1016/j.frl.2021.102604</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2785436570909961</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.038449517511149</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5076362885186358</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0035500266524496</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Financial technology</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>distance 0.3641 exceeds the cluster-1 p95 threshold 0.3588; frequency=1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>EMPIRICAL STUDY ON GAMIFICATION EFFECT ON BRAND ENGAGEMENT</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>10.51847/sAorvxedSs</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.3640547381007739</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3587503031023259</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.5328054804625619</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.0030641998720734</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 3 in corpus, z=2.27, tfidf=0.0075</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Upstarts vs incumbents: the interaction between fintech credit and bank lending in Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10.1080/23322039.2024.2375643</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5581178530369838</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.267854053430929</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6771015424689225</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0074629096558344</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alternative data</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Financial technology</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6943181050235157</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=0.34, tfidf=0.0061</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>The role of bank–FinTech partnerships in creating a more inclusive banking system</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>10.21799/frbp.wp.2023.21</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3554167823487117</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3391698830709926</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3919594342963742</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0061423532230996</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Risk-taking behavior</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6822459914777559</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>143</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=2.05, tfidf=0.0030</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Fintech-based Financial Inclusion and Risk-taking of Microfinance Institutions (MFIs): Evidence from Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10.1016/j.frl.2021.102149</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4160403358280311</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.048529493785347</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5828420140215937</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0029862148015119</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; financial innovation</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6661038066192673</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=0.66, tfidf=0.0041</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DOES FINTECH AFFECT FINANCIAL INCLUSION IN BALKAN REGION COUNTRIES?</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>10.22495/jgrv13i1siart12</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.3501876271531672</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6596497095801059</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5476971165331981</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0041047638465623</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Disadvantaged Communities</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; financial innovation</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6630721459130551</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=0.29, tfidf=0.0055</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>THE ROLE OF FINANCIAL TECHNOLOGY IN ENHANCING FINANCIAL INCLUSION: A REGULATORY PERSPECTIVE ON CURRENT INDUSTRY TRENDS</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10.22495/cbsrv6i1art4</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3160284105102336</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.285518055280809</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4808629481045412</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0054968036072316</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Banks’ risk-taking</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6598008172085355</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>195</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=-1.16, tfidf=0.0282</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Fintech-based financial inclusion and bank risk-taking: Evidence from OIC countries</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10.1016/j.intfin.2021.101447</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1598415970482152</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.155809275001417</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3830864484297354</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0281871122181571</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bank concentration</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Panel data &amp; Alternative information</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6575478011809395</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.21, tfidf=0.0037</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Does digital financial inclusion moderate or exacerbate output volatility?</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10.1080/13504851.2021.1963400</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4584609624946814</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.206184642075575</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.505308339304069</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0036878431466645</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Black swan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial technology &amp; Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6374958055320006</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>51</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.21, tfidf=0.0020</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Has financial inclusion made the financial sector riskier?</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10.1108/JFRC-08-2020-0074</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3491909563733197</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.212428351069866</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6635805922073728</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0020072232246325</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Output volatility</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Panel data &amp; Alternative information</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.632986075391512</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=0.67, tfidf=0.0037</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Does digital financial inclusion moderate or exacerbate output volatility?</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10.1080/13504851.2021.1963400</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4006583175410005</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6694097337019128</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5322524413975456</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.0036878431466645</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Big tech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Income inequality &amp; Big tech</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>44</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 1 in corpus, z=1.00, tfidf=0.0040</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Fintech credit, big tech credit and income inequality</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10.1016/j.frl.2022.103387</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3804038906307352</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4321319645328699</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.0039585973693234</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Digitalization</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5410662758628697</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 6 in corpus, z=-0.02, tfidf=0.0216</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The impact of digitalization on credit risk: the mediating role of financial inclusion (National Bank of Egypt (NBE) case study)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10.1080/1331677X.2023.2178018</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2159997698833071</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0216513816314452</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.4261859866156499</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0215682492553081</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Emerging Concept</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Digital lending</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; Digitalization</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5059078686803615</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>391</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>frequency=1 in cluster, 2 in corpus, z=0.59, tfidf=0.0068</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The rise of digital finance: Financial inclusion or debt trap?</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>10.1016/j.frl.2021.102604</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2519684540715916</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5880074699579506</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2993909863575299</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.006790361222391</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
